--- a/VerveStacks_JPN_grids_kan/Sets-vervestacks.xlsx
+++ b/VerveStacks_JPN_grids_kan/Sets-vervestacks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr updateLinks="never" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jeragroup.sharepoint.com/sites/JE_Ltd1114_JA010/DocLib1/4. 各種モデル/3. エネルギー需給モデル/03_Vervestacks Model/vervestacks_models/VerveStacks_JPN_grids_kan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{01EB8F7F-9995-4A63-B2DB-E83CE843CB96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{01EB8F7F-9995-4A63-B2DB-E83CE843CB96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E43C187E-4D1C-4258-A1C1-762198540FBD}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13800" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
@@ -2078,11 +2078,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2090,7 +2090,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2098,17 +2098,30 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -2143,16 +2156,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Heading 2" xfId="1" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="2" builtinId="18"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="見出し 2" xfId="1" builtinId="17"/>
+    <cellStyle name="見出し 3" xfId="2" builtinId="18"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2168,9 +2182,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2208,7 +2222,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2314,7 +2328,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2456,7 +2470,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2465,25 +2479,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB068F12-506D-4B74-BF24-03EBDA23C84D}">
   <dimension ref="A1:K37"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="10.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.86328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.53125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.86328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.19921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.59765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.58203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.58203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.4140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -2509,7 +2523,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" t="str">
         <f>"e_*"&amp;K3</f>
         <v>e_*220</v>
@@ -2522,7 +2536,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" t="str">
         <f t="shared" ref="B4:B23" si="1">"e_*"&amp;K4</f>
         <v>e_*400</v>
@@ -2535,7 +2549,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" t="str">
         <f t="shared" si="1"/>
         <v>e_*380</v>
@@ -2548,7 +2562,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" t="str">
         <f t="shared" si="1"/>
         <v>e_*225</v>
@@ -2561,7 +2575,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" t="str">
         <f t="shared" si="1"/>
         <v>e_*330</v>
@@ -2574,7 +2588,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" t="str">
         <f t="shared" si="1"/>
         <v>e_*275</v>
@@ -2587,7 +2601,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" t="str">
         <f t="shared" si="1"/>
         <v>e_*420</v>
@@ -2600,7 +2614,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" t="str">
         <f t="shared" si="1"/>
         <v>e_*300</v>
@@ -2613,7 +2627,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" t="str">
         <f t="shared" si="1"/>
         <v>e_*500</v>
@@ -2626,7 +2640,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" t="str">
         <f t="shared" si="1"/>
         <v>e_*750</v>
@@ -2639,7 +2653,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" t="str">
         <f t="shared" si="1"/>
         <v>e_*450</v>
@@ -2652,7 +2666,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" t="str">
         <f t="shared" si="1"/>
         <v>e_*515</v>
@@ -2665,7 +2679,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" t="str">
         <f t="shared" si="1"/>
         <v>e_*525</v>
@@ -2678,7 +2692,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" t="str">
         <f t="shared" si="1"/>
         <v>e_*320</v>
@@ -2691,7 +2705,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" t="str">
         <f t="shared" si="1"/>
         <v>e_*150</v>
@@ -2704,7 +2718,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" t="str">
         <f t="shared" si="1"/>
         <v>e_*270</v>
@@ -2717,7 +2731,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" t="str">
         <f t="shared" si="1"/>
         <v>e_*350</v>
@@ -2730,7 +2744,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" t="str">
         <f t="shared" si="1"/>
         <v>e_*250</v>
@@ -2743,7 +2757,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" t="str">
         <f t="shared" si="1"/>
         <v>e_*200</v>
@@ -2756,7 +2770,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" t="str">
         <f t="shared" si="1"/>
         <v>e_*236</v>
@@ -2769,7 +2783,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" t="str">
         <f t="shared" si="1"/>
         <v>e_*600</v>
@@ -2782,7 +2796,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B24" t="s">
         <v>44</v>
       </c>
@@ -2790,7 +2804,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" t="s">
         <v>45</v>
       </c>
@@ -2798,7 +2812,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" t="s">
         <v>60</v>
       </c>
@@ -2806,7 +2820,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B27" t="s">
         <v>61</v>
       </c>
@@ -2814,7 +2828,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" t="s">
         <v>46</v>
       </c>
@@ -2823,7 +2837,7 @@
         <v>bioenergy</v>
       </c>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" t="s">
         <v>47</v>
       </c>
@@ -2832,7 +2846,7 @@
         <v>hydrogen</v>
       </c>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B30" t="s">
         <v>36</v>
       </c>
@@ -2841,7 +2855,7 @@
         <v>nuclear</v>
       </c>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B31" t="s">
         <v>48</v>
       </c>
@@ -2850,7 +2864,7 @@
         <v>ELC</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B32" t="s">
         <v>49</v>
       </c>
@@ -2858,7 +2872,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B33" t="s">
         <v>50</v>
       </c>
@@ -2866,7 +2880,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" t="s">
         <v>51</v>
       </c>
@@ -2874,7 +2888,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B35" t="s">
         <v>52</v>
       </c>
@@ -2882,7 +2896,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B36" t="s">
         <v>53</v>
       </c>
@@ -2891,7 +2905,7 @@
         <v>co2</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B37" t="s">
         <v>54</v>
       </c>
@@ -2904,6 +2918,7 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A26:D37">
     <sortCondition ref="A26:A37"/>
   </sortState>
+  <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2911,14 +2926,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89898591-2AEA-456B-83A2-A8912B3A7DE3}">
   <dimension ref="B9:E297"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="2" width="15.58203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B9" t="s">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="3" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" t="s">
         <v>99</v>
       </c>
@@ -2932,7 +2952,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" t="s">
         <v>103</v>
       </c>
@@ -2946,7 +2966,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" t="s">
         <v>106</v>
       </c>
@@ -2960,7 +2980,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" t="s">
         <v>108</v>
       </c>
@@ -2974,7 +2994,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" t="s">
         <v>110</v>
       </c>
@@ -2988,7 +3008,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" t="s">
         <v>112</v>
       </c>
@@ -3002,7 +3022,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" t="s">
         <v>114</v>
       </c>
@@ -3016,7 +3036,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" t="s">
         <v>116</v>
       </c>
@@ -3030,7 +3050,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" t="s">
         <v>118</v>
       </c>
@@ -3044,7 +3064,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" t="s">
         <v>120</v>
       </c>
@@ -3058,7 +3078,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" t="s">
         <v>122</v>
       </c>
@@ -3072,7 +3092,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" t="s">
         <v>124</v>
       </c>
@@ -3086,7 +3106,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" t="s">
         <v>126</v>
       </c>
@@ -3100,7 +3120,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" t="s">
         <v>128</v>
       </c>
@@ -3114,7 +3134,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B24" t="s">
         <v>130</v>
       </c>
@@ -3128,7 +3148,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" t="s">
         <v>132</v>
       </c>
@@ -3142,7 +3162,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" t="s">
         <v>134</v>
       </c>
@@ -3156,7 +3176,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B27" t="s">
         <v>136</v>
       </c>
@@ -3170,7 +3190,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" t="s">
         <v>138</v>
       </c>
@@ -3184,7 +3204,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" t="s">
         <v>140</v>
       </c>
@@ -3198,7 +3218,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B30" t="s">
         <v>142</v>
       </c>
@@ -3212,7 +3232,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B31" t="s">
         <v>144</v>
       </c>
@@ -3226,7 +3246,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B32" t="s">
         <v>146</v>
       </c>
@@ -3240,7 +3260,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B33" t="s">
         <v>148</v>
       </c>
@@ -3254,7 +3274,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" t="s">
         <v>150</v>
       </c>
@@ -3268,7 +3288,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B35" t="s">
         <v>152</v>
       </c>
@@ -3282,7 +3302,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B36" t="s">
         <v>154</v>
       </c>
@@ -3296,7 +3316,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B37" t="s">
         <v>156</v>
       </c>
@@ -3310,7 +3330,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B38" t="s">
         <v>158</v>
       </c>
@@ -3324,7 +3344,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B39" t="s">
         <v>160</v>
       </c>
@@ -3338,7 +3358,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B40" t="s">
         <v>162</v>
       </c>
@@ -3352,7 +3372,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B41" t="s">
         <v>164</v>
       </c>
@@ -3366,7 +3386,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B42" t="s">
         <v>166</v>
       </c>
@@ -3380,7 +3400,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B43" t="s">
         <v>168</v>
       </c>
@@ -3394,7 +3414,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B44" t="s">
         <v>170</v>
       </c>
@@ -3408,7 +3428,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" t="s">
         <v>172</v>
       </c>
@@ -3422,7 +3442,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B46" t="s">
         <v>174</v>
       </c>
@@ -3436,7 +3456,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B47" t="s">
         <v>176</v>
       </c>
@@ -3450,7 +3470,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B48" t="s">
         <v>178</v>
       </c>
@@ -3464,7 +3484,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B49" t="s">
         <v>180</v>
       </c>
@@ -3478,7 +3498,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B50" t="s">
         <v>182</v>
       </c>
@@ -3492,7 +3512,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B51" t="s">
         <v>184</v>
       </c>
@@ -3506,7 +3526,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B52" t="s">
         <v>186</v>
       </c>
@@ -3520,7 +3540,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B53" t="s">
         <v>188</v>
       </c>
@@ -3534,7 +3554,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B54" t="s">
         <v>190</v>
       </c>
@@ -3548,7 +3568,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B55" t="s">
         <v>192</v>
       </c>
@@ -3562,7 +3582,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B56" t="s">
         <v>194</v>
       </c>
@@ -3576,7 +3596,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B57" t="s">
         <v>196</v>
       </c>
@@ -3590,7 +3610,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B58" t="s">
         <v>198</v>
       </c>
@@ -3604,7 +3624,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B59" t="s">
         <v>200</v>
       </c>
@@ -3618,7 +3638,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B60" t="s">
         <v>202</v>
       </c>
@@ -3632,7 +3652,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B61" t="s">
         <v>204</v>
       </c>
@@ -3646,7 +3666,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B62" t="s">
         <v>206</v>
       </c>
@@ -3660,7 +3680,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B63" t="s">
         <v>208</v>
       </c>
@@ -3674,7 +3694,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B64" t="s">
         <v>210</v>
       </c>
@@ -3688,7 +3708,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B65" t="s">
         <v>212</v>
       </c>
@@ -3702,7 +3722,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B66" t="s">
         <v>214</v>
       </c>
@@ -3716,7 +3736,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B67" t="s">
         <v>216</v>
       </c>
@@ -3730,7 +3750,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B68" t="s">
         <v>218</v>
       </c>
@@ -3744,7 +3764,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B69" t="s">
         <v>220</v>
       </c>
@@ -3758,7 +3778,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B70" t="s">
         <v>222</v>
       </c>
@@ -3772,7 +3792,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B71" t="s">
         <v>224</v>
       </c>
@@ -3786,7 +3806,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B72" t="s">
         <v>226</v>
       </c>
@@ -3800,7 +3820,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B73" t="s">
         <v>228</v>
       </c>
@@ -3814,7 +3834,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B74" t="s">
         <v>230</v>
       </c>
@@ -3828,7 +3848,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B75" t="s">
         <v>232</v>
       </c>
@@ -3842,7 +3862,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B76" t="s">
         <v>234</v>
       </c>
@@ -3856,7 +3876,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="77" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B77" t="s">
         <v>236</v>
       </c>
@@ -3870,7 +3890,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="78" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B78" t="s">
         <v>238</v>
       </c>
@@ -3884,7 +3904,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="79" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B79" t="s">
         <v>240</v>
       </c>
@@ -3898,7 +3918,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="80" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B80" t="s">
         <v>242</v>
       </c>
@@ -3912,7 +3932,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B81" t="s">
         <v>244</v>
       </c>
@@ -3926,7 +3946,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B82" t="s">
         <v>246</v>
       </c>
@@ -3940,7 +3960,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B83" t="s">
         <v>248</v>
       </c>
@@ -3954,7 +3974,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B84" t="s">
         <v>250</v>
       </c>
@@ -3968,7 +3988,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B85" t="s">
         <v>252</v>
       </c>
@@ -3982,7 +4002,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B86" t="s">
         <v>254</v>
       </c>
@@ -3996,7 +4016,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B87" t="s">
         <v>256</v>
       </c>
@@ -4010,7 +4030,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B88" t="s">
         <v>258</v>
       </c>
@@ -4024,7 +4044,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B89" t="s">
         <v>260</v>
       </c>
@@ -4038,7 +4058,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B90" t="s">
         <v>262</v>
       </c>
@@ -4052,7 +4072,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B91" t="s">
         <v>264</v>
       </c>
@@ -4066,7 +4086,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B92" t="s">
         <v>266</v>
       </c>
@@ -4080,7 +4100,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B93" t="s">
         <v>268</v>
       </c>
@@ -4094,7 +4114,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B94" t="s">
         <v>270</v>
       </c>
@@ -4108,7 +4128,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B95" t="s">
         <v>272</v>
       </c>
@@ -4122,7 +4142,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="96" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B96" t="s">
         <v>274</v>
       </c>
@@ -4136,7 +4156,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="97" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B97" t="s">
         <v>276</v>
       </c>
@@ -4150,7 +4170,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="98" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B98" t="s">
         <v>278</v>
       </c>
@@ -4164,7 +4184,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="99" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B99" t="s">
         <v>280</v>
       </c>
@@ -4178,7 +4198,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="100" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B100" t="s">
         <v>282</v>
       </c>
@@ -4192,7 +4212,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="101" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B101" t="s">
         <v>284</v>
       </c>
@@ -4206,7 +4226,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="102" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B102" t="s">
         <v>286</v>
       </c>
@@ -4220,7 +4240,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="103" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B103" t="s">
         <v>288</v>
       </c>
@@ -4234,7 +4254,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="104" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B104" t="s">
         <v>290</v>
       </c>
@@ -4248,7 +4268,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="105" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B105" t="s">
         <v>292</v>
       </c>
@@ -4262,7 +4282,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="106" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B106" t="s">
         <v>294</v>
       </c>
@@ -4276,7 +4296,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="107" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B107" t="s">
         <v>296</v>
       </c>
@@ -4290,7 +4310,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="108" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="108" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B108" t="s">
         <v>298</v>
       </c>
@@ -4304,7 +4324,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="109" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="109" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B109" t="s">
         <v>300</v>
       </c>
@@ -4318,7 +4338,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="110" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="110" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B110" t="s">
         <v>302</v>
       </c>
@@ -4332,7 +4352,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="111" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="111" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B111" t="s">
         <v>304</v>
       </c>
@@ -4346,7 +4366,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="112" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="112" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B112" t="s">
         <v>306</v>
       </c>
@@ -4360,7 +4380,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="113" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="113" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B113" t="s">
         <v>308</v>
       </c>
@@ -4374,7 +4394,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="114" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="114" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B114" t="s">
         <v>310</v>
       </c>
@@ -4388,7 +4408,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="115" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="115" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B115" t="s">
         <v>312</v>
       </c>
@@ -4402,7 +4422,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="116" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="116" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B116" t="s">
         <v>314</v>
       </c>
@@ -4416,7 +4436,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="117" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="117" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B117" t="s">
         <v>316</v>
       </c>
@@ -4430,7 +4450,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="118" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="118" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B118" t="s">
         <v>318</v>
       </c>
@@ -4444,7 +4464,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="119" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="119" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B119" t="s">
         <v>320</v>
       </c>
@@ -4458,7 +4478,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="120" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="120" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B120" t="s">
         <v>322</v>
       </c>
@@ -4472,7 +4492,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="121" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="121" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B121" t="s">
         <v>324</v>
       </c>
@@ -4486,7 +4506,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="122" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="122" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B122" t="s">
         <v>326</v>
       </c>
@@ -4500,7 +4520,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="123" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="123" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B123" t="s">
         <v>328</v>
       </c>
@@ -4514,7 +4534,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="124" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="124" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B124" t="s">
         <v>330</v>
       </c>
@@ -4528,7 +4548,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="125" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="125" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B125" t="s">
         <v>332</v>
       </c>
@@ -4542,7 +4562,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="126" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="126" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B126" t="s">
         <v>334</v>
       </c>
@@ -4556,7 +4576,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="127" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="127" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B127" t="s">
         <v>336</v>
       </c>
@@ -4570,7 +4590,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="128" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="128" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B128" t="s">
         <v>338</v>
       </c>
@@ -4584,7 +4604,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="129" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="129" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B129" t="s">
         <v>340</v>
       </c>
@@ -4598,7 +4618,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="130" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="130" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B130" t="s">
         <v>342</v>
       </c>
@@ -4612,7 +4632,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="131" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="131" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B131" t="s">
         <v>344</v>
       </c>
@@ -4626,7 +4646,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="132" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="132" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B132" t="s">
         <v>346</v>
       </c>
@@ -4640,7 +4660,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="133" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="133" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B133" t="s">
         <v>348</v>
       </c>
@@ -4654,7 +4674,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="134" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="134" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B134" t="s">
         <v>350</v>
       </c>
@@ -4668,7 +4688,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="135" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="135" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B135" t="s">
         <v>352</v>
       </c>
@@ -4682,7 +4702,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="136" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="136" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B136" t="s">
         <v>354</v>
       </c>
@@ -4696,7 +4716,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="137" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="137" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B137" t="s">
         <v>356</v>
       </c>
@@ -4710,7 +4730,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="138" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="138" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B138" t="s">
         <v>358</v>
       </c>
@@ -4724,7 +4744,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="139" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="139" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B139" t="s">
         <v>360</v>
       </c>
@@ -4738,7 +4758,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="140" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="140" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B140" t="s">
         <v>362</v>
       </c>
@@ -4752,7 +4772,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="141" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="141" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B141" t="s">
         <v>364</v>
       </c>
@@ -4766,7 +4786,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="142" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="142" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B142" t="s">
         <v>366</v>
       </c>
@@ -4780,7 +4800,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="143" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="143" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B143" t="s">
         <v>368</v>
       </c>
@@ -4794,7 +4814,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="144" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="144" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B144" t="s">
         <v>370</v>
       </c>
@@ -4808,7 +4828,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="145" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="145" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B145" t="s">
         <v>372</v>
       </c>
@@ -4822,7 +4842,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="146" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="146" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B146" t="s">
         <v>374</v>
       </c>
@@ -4836,7 +4856,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="147" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="147" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B147" t="s">
         <v>376</v>
       </c>
@@ -4850,7 +4870,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="148" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="148" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B148" t="s">
         <v>378</v>
       </c>
@@ -4864,7 +4884,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="149" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="149" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B149" t="s">
         <v>380</v>
       </c>
@@ -4878,7 +4898,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="150" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="150" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B150" t="s">
         <v>382</v>
       </c>
@@ -4892,7 +4912,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="151" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="151" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B151" t="s">
         <v>384</v>
       </c>
@@ -4906,7 +4926,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="152" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="152" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B152" t="s">
         <v>386</v>
       </c>
@@ -4920,7 +4940,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="153" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="153" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B153" t="s">
         <v>388</v>
       </c>
@@ -4934,7 +4954,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="154" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="154" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B154" t="s">
         <v>390</v>
       </c>
@@ -4948,7 +4968,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="155" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="155" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B155" t="s">
         <v>392</v>
       </c>
@@ -4962,7 +4982,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="156" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="156" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B156" t="s">
         <v>394</v>
       </c>
@@ -4976,7 +4996,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="157" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="157" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B157" t="s">
         <v>396</v>
       </c>
@@ -4990,7 +5010,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="158" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="158" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B158" t="s">
         <v>398</v>
       </c>
@@ -5004,7 +5024,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="159" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="159" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B159" t="s">
         <v>400</v>
       </c>
@@ -5018,7 +5038,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="160" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="160" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B160" t="s">
         <v>402</v>
       </c>
@@ -5032,7 +5052,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="161" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="161" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B161" t="s">
         <v>404</v>
       </c>
@@ -5046,7 +5066,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="162" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="162" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B162" t="s">
         <v>406</v>
       </c>
@@ -5060,7 +5080,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="163" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="163" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B163" t="s">
         <v>408</v>
       </c>
@@ -5074,7 +5094,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="164" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="164" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B164" t="s">
         <v>410</v>
       </c>
@@ -5088,7 +5108,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="165" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="165" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B165" t="s">
         <v>412</v>
       </c>
@@ -5102,7 +5122,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="166" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="166" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B166" t="s">
         <v>414</v>
       </c>
@@ -5116,7 +5136,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="167" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="167" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B167" t="s">
         <v>416</v>
       </c>
@@ -5130,7 +5150,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="168" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="168" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B168" t="s">
         <v>418</v>
       </c>
@@ -5144,7 +5164,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="169" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="169" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B169" t="s">
         <v>420</v>
       </c>
@@ -5158,7 +5178,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="170" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="170" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B170" t="s">
         <v>422</v>
       </c>
@@ -5172,7 +5192,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="171" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="171" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B171" t="s">
         <v>424</v>
       </c>
@@ -5186,7 +5206,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="172" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="172" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B172" t="s">
         <v>426</v>
       </c>
@@ -5200,7 +5220,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="173" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="173" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B173" t="s">
         <v>428</v>
       </c>
@@ -5214,7 +5234,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="174" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="174" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B174" t="s">
         <v>430</v>
       </c>
@@ -5228,7 +5248,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="175" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="175" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B175" t="s">
         <v>432</v>
       </c>
@@ -5242,7 +5262,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="176" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="176" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B176" t="s">
         <v>434</v>
       </c>
@@ -5256,7 +5276,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="177" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="177" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B177" t="s">
         <v>436</v>
       </c>
@@ -5270,7 +5290,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="178" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="178" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B178" t="s">
         <v>438</v>
       </c>
@@ -5284,7 +5304,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="179" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="179" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B179" t="s">
         <v>440</v>
       </c>
@@ -5298,7 +5318,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="180" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="180" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B180" t="s">
         <v>442</v>
       </c>
@@ -5312,7 +5332,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="181" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="181" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B181" t="s">
         <v>444</v>
       </c>
@@ -5326,7 +5346,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="182" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="182" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B182" t="s">
         <v>446</v>
       </c>
@@ -5340,7 +5360,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="183" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="183" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B183" t="s">
         <v>448</v>
       </c>
@@ -5354,7 +5374,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="184" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="184" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B184" t="s">
         <v>450</v>
       </c>
@@ -5368,7 +5388,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="185" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="185" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B185" t="s">
         <v>452</v>
       </c>
@@ -5382,7 +5402,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="186" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="186" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B186" t="s">
         <v>454</v>
       </c>
@@ -5396,7 +5416,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="187" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="187" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B187" t="s">
         <v>456</v>
       </c>
@@ -5410,7 +5430,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="188" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="188" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B188" t="s">
         <v>458</v>
       </c>
@@ -5424,7 +5444,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="189" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="189" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B189" t="s">
         <v>460</v>
       </c>
@@ -5438,7 +5458,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="190" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="190" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B190" t="s">
         <v>462</v>
       </c>
@@ -5452,7 +5472,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="191" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="191" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B191" t="s">
         <v>464</v>
       </c>
@@ -5466,7 +5486,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="192" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="192" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B192" t="s">
         <v>466</v>
       </c>
@@ -5480,7 +5500,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="193" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="193" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B193" t="s">
         <v>468</v>
       </c>
@@ -5494,7 +5514,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="194" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="194" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B194" t="s">
         <v>470</v>
       </c>
@@ -5508,7 +5528,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="195" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="195" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B195" t="s">
         <v>472</v>
       </c>
@@ -5522,7 +5542,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="196" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="196" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B196" t="s">
         <v>474</v>
       </c>
@@ -5536,7 +5556,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="197" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="197" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B197" t="s">
         <v>476</v>
       </c>
@@ -5550,7 +5570,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="198" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="198" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B198" t="s">
         <v>478</v>
       </c>
@@ -5564,7 +5584,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="199" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="199" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B199" t="s">
         <v>480</v>
       </c>
@@ -5578,7 +5598,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="200" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="200" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B200" t="s">
         <v>482</v>
       </c>
@@ -5592,7 +5612,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="201" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="201" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B201" t="s">
         <v>484</v>
       </c>
@@ -5606,7 +5626,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="202" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="202" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B202" t="s">
         <v>486</v>
       </c>
@@ -5620,7 +5640,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="203" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="203" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B203" t="s">
         <v>488</v>
       </c>
@@ -5634,7 +5654,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="204" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="204" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B204" t="s">
         <v>490</v>
       </c>
@@ -5648,7 +5668,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="205" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="205" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B205" t="s">
         <v>492</v>
       </c>
@@ -5662,7 +5682,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="206" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="206" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B206" t="s">
         <v>494</v>
       </c>
@@ -5676,7 +5696,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="207" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="207" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B207" t="s">
         <v>496</v>
       </c>
@@ -5690,7 +5710,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="208" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="208" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B208" t="s">
         <v>498</v>
       </c>
@@ -5704,7 +5724,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="209" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="209" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B209" t="s">
         <v>500</v>
       </c>
@@ -5718,7 +5738,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="210" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="210" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B210" t="s">
         <v>502</v>
       </c>
@@ -5732,7 +5752,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="211" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="211" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B211" t="s">
         <v>504</v>
       </c>
@@ -5746,7 +5766,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="212" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="212" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B212" t="s">
         <v>506</v>
       </c>
@@ -5760,7 +5780,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="213" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="213" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B213" t="s">
         <v>508</v>
       </c>
@@ -5774,7 +5794,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="214" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="214" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B214" t="s">
         <v>510</v>
       </c>
@@ -5788,7 +5808,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="215" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="215" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B215" t="s">
         <v>512</v>
       </c>
@@ -5802,7 +5822,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="216" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="216" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B216" t="s">
         <v>514</v>
       </c>
@@ -5816,7 +5836,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="217" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="217" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B217" t="s">
         <v>516</v>
       </c>
@@ -5830,7 +5850,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="218" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="218" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B218" t="s">
         <v>518</v>
       </c>
@@ -5844,7 +5864,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="219" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="219" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B219" t="s">
         <v>520</v>
       </c>
@@ -5858,7 +5878,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="220" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="220" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B220" t="s">
         <v>522</v>
       </c>
@@ -5872,7 +5892,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="221" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="221" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B221" t="s">
         <v>524</v>
       </c>
@@ -5886,7 +5906,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="222" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="222" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B222" t="s">
         <v>526</v>
       </c>
@@ -5900,7 +5920,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="223" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="223" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B223" t="s">
         <v>528</v>
       </c>
@@ -5914,7 +5934,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="224" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="224" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B224" t="s">
         <v>530</v>
       </c>
@@ -5928,7 +5948,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="225" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="225" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B225" t="s">
         <v>532</v>
       </c>
@@ -5942,7 +5962,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="226" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="226" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B226" t="s">
         <v>534</v>
       </c>
@@ -5956,7 +5976,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="227" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="227" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B227" t="s">
         <v>536</v>
       </c>
@@ -5970,7 +5990,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="228" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="228" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B228" t="s">
         <v>538</v>
       </c>
@@ -5984,7 +6004,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="229" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="229" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B229" t="s">
         <v>540</v>
       </c>
@@ -5998,7 +6018,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="230" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="230" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B230" t="s">
         <v>542</v>
       </c>
@@ -6012,7 +6032,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="231" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="231" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B231" t="s">
         <v>544</v>
       </c>
@@ -6026,7 +6046,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="232" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="232" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B232" t="s">
         <v>546</v>
       </c>
@@ -6040,7 +6060,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="233" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="233" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B233" t="s">
         <v>548</v>
       </c>
@@ -6054,7 +6074,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="234" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="234" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B234" t="s">
         <v>550</v>
       </c>
@@ -6068,7 +6088,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="235" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="235" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B235" t="s">
         <v>552</v>
       </c>
@@ -6082,7 +6102,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="236" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="236" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B236" t="s">
         <v>554</v>
       </c>
@@ -6096,7 +6116,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="237" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="237" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B237" t="s">
         <v>556</v>
       </c>
@@ -6110,7 +6130,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="238" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="238" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B238" t="s">
         <v>558</v>
       </c>
@@ -6124,7 +6144,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="239" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="239" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B239" t="s">
         <v>560</v>
       </c>
@@ -6138,7 +6158,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="240" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="240" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B240" t="s">
         <v>562</v>
       </c>
@@ -6152,7 +6172,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="241" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="241" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B241" t="s">
         <v>564</v>
       </c>
@@ -6166,7 +6186,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="242" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="242" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B242" t="s">
         <v>566</v>
       </c>
@@ -6180,7 +6200,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="243" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="243" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B243" t="s">
         <v>568</v>
       </c>
@@ -6194,7 +6214,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="244" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="244" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B244" t="s">
         <v>570</v>
       </c>
@@ -6208,7 +6228,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="245" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="245" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B245" t="s">
         <v>572</v>
       </c>
@@ -6222,7 +6242,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="246" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="246" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B246" t="s">
         <v>574</v>
       </c>
@@ -6236,7 +6256,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="247" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="247" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B247" t="s">
         <v>576</v>
       </c>
@@ -6250,7 +6270,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="248" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="248" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B248" t="s">
         <v>578</v>
       </c>
@@ -6264,7 +6284,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="249" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="249" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B249" t="s">
         <v>580</v>
       </c>
@@ -6278,7 +6298,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="250" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="250" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B250" t="s">
         <v>582</v>
       </c>
@@ -6292,7 +6312,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="251" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="251" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B251" t="s">
         <v>584</v>
       </c>
@@ -6306,7 +6326,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="252" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="252" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B252" t="s">
         <v>586</v>
       </c>
@@ -6320,7 +6340,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="253" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="253" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B253" t="s">
         <v>588</v>
       </c>
@@ -6334,7 +6354,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="254" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="254" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B254" t="s">
         <v>590</v>
       </c>
@@ -6348,7 +6368,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="255" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="255" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B255" t="s">
         <v>592</v>
       </c>
@@ -6362,7 +6382,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="256" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="256" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B256" t="s">
         <v>594</v>
       </c>
@@ -6376,7 +6396,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="257" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="257" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B257" t="s">
         <v>596</v>
       </c>
@@ -6390,7 +6410,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="258" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="258" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B258" t="s">
         <v>598</v>
       </c>
@@ -6404,7 +6424,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="259" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="259" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B259" t="s">
         <v>600</v>
       </c>
@@ -6418,7 +6438,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="260" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="260" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B260" t="s">
         <v>602</v>
       </c>
@@ -6432,7 +6452,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="261" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="261" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B261" t="s">
         <v>604</v>
       </c>
@@ -6446,7 +6466,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="262" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="262" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B262" t="s">
         <v>606</v>
       </c>
@@ -6460,7 +6480,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="263" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="263" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B263" t="s">
         <v>608</v>
       </c>
@@ -6474,7 +6494,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="264" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="264" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B264" t="s">
         <v>610</v>
       </c>
@@ -6488,7 +6508,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="265" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="265" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B265" t="s">
         <v>612</v>
       </c>
@@ -6502,7 +6522,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="266" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="266" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B266" t="s">
         <v>614</v>
       </c>
@@ -6516,7 +6536,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="267" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="267" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B267" t="s">
         <v>616</v>
       </c>
@@ -6530,7 +6550,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="268" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="268" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B268" t="s">
         <v>618</v>
       </c>
@@ -6544,7 +6564,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="269" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="269" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B269" t="s">
         <v>620</v>
       </c>
@@ -6558,7 +6578,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="270" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="270" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B270" t="s">
         <v>622</v>
       </c>
@@ -6572,7 +6592,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="271" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="271" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B271" t="s">
         <v>624</v>
       </c>
@@ -6586,7 +6606,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="272" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="272" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B272" t="s">
         <v>626</v>
       </c>
@@ -6600,7 +6620,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="273" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="273" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B273" t="s">
         <v>628</v>
       </c>
@@ -6614,7 +6634,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="274" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="274" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B274" t="s">
         <v>630</v>
       </c>
@@ -6628,7 +6648,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="275" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="275" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B275" t="s">
         <v>632</v>
       </c>
@@ -6642,7 +6662,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="276" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="276" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B276" t="s">
         <v>634</v>
       </c>
@@ -6656,7 +6676,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="277" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="277" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B277" t="s">
         <v>636</v>
       </c>
@@ -6670,7 +6690,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="278" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="278" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B278" t="s">
         <v>638</v>
       </c>
@@ -6684,7 +6704,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="279" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="279" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B279" t="s">
         <v>640</v>
       </c>
@@ -6698,7 +6718,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="280" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="280" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B280" t="s">
         <v>642</v>
       </c>
@@ -6712,7 +6732,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="281" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="281" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B281" t="s">
         <v>644</v>
       </c>
@@ -6726,7 +6746,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="282" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="282" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B282" t="s">
         <v>646</v>
       </c>
@@ -6740,7 +6760,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="283" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="283" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B283" t="s">
         <v>648</v>
       </c>
@@ -6754,7 +6774,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="284" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="284" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B284" t="s">
         <v>650</v>
       </c>
@@ -6768,7 +6788,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="285" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="285" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B285" t="s">
         <v>652</v>
       </c>
@@ -6782,7 +6802,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="286" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="286" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B286" t="s">
         <v>654</v>
       </c>
@@ -6796,7 +6816,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="287" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="287" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B287" t="s">
         <v>656</v>
       </c>
@@ -6810,7 +6830,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="288" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="288" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B288" t="s">
         <v>658</v>
       </c>
@@ -6824,7 +6844,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="289" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="289" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B289" t="s">
         <v>660</v>
       </c>
@@ -6838,7 +6858,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="290" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="290" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B290" t="s">
         <v>662</v>
       </c>
@@ -6852,7 +6872,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="291" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="291" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B291" t="s">
         <v>664</v>
       </c>
@@ -6866,7 +6886,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="292" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="292" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B292" t="s">
         <v>666</v>
       </c>
@@ -6880,7 +6900,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="293" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="293" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B293" t="s">
         <v>668</v>
       </c>
@@ -6894,7 +6914,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="294" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="294" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B294" t="s">
         <v>670</v>
       </c>
@@ -6908,7 +6928,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="295" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="295" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B295" t="s">
         <v>672</v>
       </c>
@@ -6922,7 +6942,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="296" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="296" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B296" t="s">
         <v>674</v>
       </c>
@@ -6936,7 +6956,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="297" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="297" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B297" t="s">
         <v>676</v>
       </c>
@@ -6951,60 +6971,67 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71754C8A-E599-4286-919F-11B5789CC171}">
   <dimension ref="A1:K48"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="2" width="86" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.59765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.86328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.58203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="57" customWidth="1"/>
+    <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.08203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" ht="22" thickBot="1" x14ac:dyDescent="0.7">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:10" ht="19" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" t="s">
         <v>91</v>
       </c>
@@ -7021,7 +7048,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" t="s">
         <v>92</v>
       </c>
@@ -7029,7 +7056,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" t="s">
         <v>93</v>
       </c>
@@ -7037,7 +7064,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" t="s">
         <v>94</v>
       </c>
@@ -7051,7 +7078,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" t="s">
         <v>95</v>
       </c>
@@ -7059,7 +7086,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" t="s">
         <v>96</v>
       </c>
@@ -7067,7 +7094,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" t="s">
         <v>26</v>
       </c>
@@ -7075,7 +7102,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" t="s">
         <v>97</v>
       </c>
@@ -7083,7 +7110,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="D11" t="s">
         <v>33</v>
       </c>
@@ -7091,8 +7118,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="B12" s="3"/>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="2"/>
       <c r="D12" t="s">
         <v>84</v>
       </c>
@@ -7103,7 +7130,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="D13" t="s">
         <v>85</v>
       </c>
@@ -7114,7 +7141,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="D14" t="s">
         <v>34</v>
       </c>
@@ -7122,11 +7149,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>73</v>
       </c>
       <c r="D15" t="s">
@@ -7136,7 +7163,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -7150,8 +7177,8 @@
         <v>66</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="B17" s="3" t="s">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" s="2" t="s">
         <v>72</v>
       </c>
       <c r="D17" t="s">
@@ -7167,7 +7194,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" t="s">
         <v>70</v>
       </c>
@@ -7178,7 +7205,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -7189,7 +7216,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -7206,7 +7233,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -7217,7 +7244,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -7228,7 +7255,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>42</v>
       </c>
@@ -7236,7 +7263,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>62</v>
       </c>
@@ -7247,7 +7274,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -7258,7 +7285,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" t="str">
         <f>"g[_]*"&amp;K26</f>
         <v>g[_]*220</v>
@@ -7271,7 +7298,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B27" t="str">
         <f t="shared" ref="B27:B46" si="0">"g[_]*"&amp;K27</f>
         <v>g[_]*400</v>
@@ -7284,7 +7311,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*380</v>
@@ -7297,7 +7324,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*225</v>
@@ -7310,7 +7337,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B30" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*330</v>
@@ -7323,7 +7350,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B31" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*275</v>
@@ -7336,7 +7363,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B32" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*420</v>
@@ -7349,7 +7376,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B33" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*300</v>
@@ -7362,7 +7389,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*500</v>
@@ -7375,7 +7402,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B35" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*750</v>
@@ -7388,7 +7415,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B36" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*450</v>
@@ -7401,7 +7428,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B37" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*515</v>
@@ -7414,7 +7441,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B38" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*525</v>
@@ -7427,7 +7454,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B39" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*320</v>
@@ -7440,7 +7467,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B40" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*150</v>
@@ -7453,7 +7480,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B41" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*270</v>
@@ -7466,7 +7493,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B42" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*350</v>
@@ -7479,7 +7506,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B43" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*250</v>
@@ -7492,7 +7519,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B44" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*200</v>
@@ -7505,7 +7532,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*236</v>
@@ -7518,7 +7545,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B46" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*600</v>
@@ -7531,7 +7558,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B47" t="s">
         <v>90</v>
       </c>
@@ -7539,7 +7566,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B48" t="s">
         <v>79</v>
       </c>
@@ -7548,6 +7575,272 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="961b6814-c230-4269-82bd-def8d4313a06">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="bab054b8-c314-4c35-aaad-e6094b2a3aec" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101002DB47EE0E92B004DA587A5AC06BCAB72" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="cff8d2101153e857ff4355cc66cd45e5">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="961b6814-c230-4269-82bd-def8d4313a06" xmlns:ns3="bab054b8-c314-4c35-aaad-e6094b2a3aec" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a602de66b0b03817e42d2b6948bbd6d9" ns2:_="" ns3:_="">
+    <xsd:import namespace="961b6814-c230-4269-82bd-def8d4313a06"/>
+    <xsd:import namespace="bab054b8-c314-4c35-aaad-e6094b2a3aec"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="961b6814-c230-4269-82bd-def8d4313a06" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="画像タグ" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="761ec606-d3f6-431d-aca1-879ead0541e3" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="20" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="bab054b8-c314-4c35-aaad-e6094b2a3aec" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{fd7fabe0-2dba-4629-88b9-b2647f7a99db}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="bab054b8-c314-4c35-aaad-e6094b2a3aec">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="コンテンツ タイプ"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="タイトル"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B48881AD-D31E-4204-95C5-2C8A4817646E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="961b6814-c230-4269-82bd-def8d4313a06"/>
+    <ds:schemaRef ds:uri="bab054b8-c314-4c35-aaad-e6094b2a3aec"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{943382D7-7A4B-41A8-A707-4696FEC18D95}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{850D57E7-531D-41AC-B295-B18CACF67BF7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="961b6814-c230-4269-82bd-def8d4313a06"/>
+    <ds:schemaRef ds:uri="bab054b8-c314-4c35-aaad-e6094b2a3aec"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>